--- a/40_Threshold_OUTPUT/reverse_C1F978_Rhodobacter_sphaeroides_2_4_1.xlsx
+++ b/40_Threshold_OUTPUT/reverse_C1F978_Rhodobacter_sphaeroides_2_4_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.9856057576969213</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -586,6 +601,11 @@
       <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -663,6 +688,11 @@
       </c>
       <c r="I6" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/40_Threshold_OUTPUT/reverse_C1F978_Rhodobacter_sphaeroides_2_4_1.xlsx
+++ b/40_Threshold_OUTPUT/reverse_C1F978_Rhodobacter_sphaeroides_2_4_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -606,6 +617,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -650,6 +664,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -693,6 +710,9 @@
         <is>
           <t>Ambiguous IR</t>
         </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
